--- a/AI_AuditLog.xlsx
+++ b/AI_AuditLog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1.FPT\2026\SU26\MMA301\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13AC490B-60C7-4EB0-B2A4-ECD77CC72A0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A79854A-09BB-4ED1-8597-F2BE259F336C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AI_AuditLog" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
   <si>
     <t>Buổi</t>
   </si>
@@ -43,22 +43,25 @@
     <t>Tên hình minh chứng</t>
   </si>
   <si>
-    <t>21/05/2026</t>
-  </si>
-  <si>
-    <t>Thiết kế database booking workshop</t>
-  </si>
-  <si>
-    <t>Thiết kế database cho hệ thống booking workshop có timeslot</t>
-  </si>
-  <si>
-    <t>AI gợi ý các bảng workshops, schedules, bookings</t>
-  </si>
-  <si>
-    <t>Hiểu rõ hơn về thiết kế booking system</t>
-  </si>
-  <si>
-    <t>db-design.png</t>
+    <t>Thiết kế UI bài tập thầy cho</t>
+  </si>
+  <si>
+    <t>Hãy gợi ý cho tôi vài mẫu giao diện AI</t>
+  </si>
+  <si>
+    <t>AI gợi ý các giao diện bằng html để kham khảo</t>
+  </si>
+  <si>
+    <t>Tham gia lớp học và cùng làm bài tập thầy giao</t>
+  </si>
+  <si>
+    <t>Giải thích thay đổi chỗ nào và tại sao lại vậy</t>
+  </si>
+  <si>
+    <t>Hiểu rõ hơn về thiết kế giao diện</t>
+  </si>
+  <si>
+    <t>Hãy chỉ rõ và giải thích các phần cần thay đổi về chế độ sáng tối</t>
   </si>
 </sst>
 </file>
@@ -99,9 +102,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -117,6 +128,187 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>2</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>795062</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>1722828</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6CBD3D24-4C57-52E1-84B9-AE155C66A60A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14291437" y="181056"/>
+          <a:ext cx="795061" cy="1722826"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1001097</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>155512</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1804078</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>1676716</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6B08A85-D621-E669-338A-53966FE35963}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15292533" y="155512"/>
+          <a:ext cx="802981" cy="1702258"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>789333</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>1660260</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D4CB647-D6A3-A85F-C883-051FBAED3F7B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14565314" y="1971146"/>
+          <a:ext cx="789332" cy="1660260"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1041798</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>29766</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1809750</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>1672509</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44FB9ADA-74E8-AE49-675F-DBC0D6855B4C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15609096" y="2006204"/>
+          <a:ext cx="767952" cy="1642743"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -404,19 +596,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="50" customWidth="1"/>
-    <col min="5" max="5" width="45" customWidth="1"/>
-    <col min="6" max="6" width="40" customWidth="1"/>
-    <col min="7" max="7" width="30" customWidth="1"/>
+    <col min="1" max="1" width="10" style="2" customWidth="1"/>
+    <col min="2" max="2" width="15" style="2" customWidth="1"/>
+    <col min="3" max="3" width="40" style="2" customWidth="1"/>
+    <col min="4" max="4" width="53.9296875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="45" style="2" customWidth="1"/>
+    <col min="6" max="6" width="40" style="2" customWidth="1"/>
+    <col min="7" max="7" width="30" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.06640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -439,30 +632,48 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="2" spans="1:7" ht="141.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="3">
+        <v>46162</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="133.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3">
+        <v>46164</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G2" t="s">
+      <c r="F3" s="2" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>